--- a/02_Zero_Shot/outputs/LLM/GPT/RESULT_clap_gpt-4o_zeroshot.xlsx
+++ b/02_Zero_Shot/outputs/LLM/GPT/RESULT_clap_gpt-4o_zeroshot.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3315,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -4828,7 +4828,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -5593,7 +5593,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6545,7 +6545,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -6613,7 +6613,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6783,7 +6783,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6936,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -6987,7 +6987,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7157,7 +7157,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7293,7 +7293,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7378,7 +7378,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7463,7 +7463,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -7514,7 +7514,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7616,7 +7616,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7633,7 +7633,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7820,7 +7820,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7871,7 +7871,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7905,7 +7905,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -7922,7 +7922,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -8007,7 +8007,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8041,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -8109,7 +8109,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -8177,7 +8177,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -8381,7 +8381,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -8772,7 +8772,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -8857,7 +8857,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -9044,7 +9044,7 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -9095,7 +9095,7 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -9146,7 +9146,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -9401,7 +9401,7 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -9503,7 +9503,7 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -9571,7 +9571,7 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -9707,7 +9707,7 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -9758,7 +9758,7 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -9877,7 +9877,7 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -10013,7 +10013,7 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -10166,7 +10166,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -10438,7 +10438,7 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -10455,7 +10455,7 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -10540,7 +10540,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -10880,7 +10880,7 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -10914,7 +10914,7 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -10931,7 +10931,7 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -11084,7 +11084,7 @@
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -11152,7 +11152,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -11220,7 +11220,7 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -11237,7 +11237,7 @@
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -11305,7 +11305,7 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -11322,7 +11322,7 @@
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -11339,7 +11339,7 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -11356,7 +11356,7 @@
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -11373,7 +11373,7 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -11441,7 +11441,7 @@
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -11645,7 +11645,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -12053,7 +12053,7 @@
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12070,7 +12070,7 @@
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12155,7 +12155,7 @@
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12240,7 +12240,7 @@
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -12359,7 +12359,7 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12478,7 +12478,7 @@
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12665,7 +12665,7 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12750,7 +12750,7 @@
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12784,7 +12784,7 @@
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12886,7 +12886,7 @@
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12903,7 +12903,7 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12920,7 +12920,7 @@
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -12937,7 +12937,7 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -13073,7 +13073,7 @@
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -13090,7 +13090,7 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -13175,7 +13175,7 @@
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -13192,7 +13192,7 @@
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -13226,7 +13226,7 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -13277,7 +13277,7 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -13396,7 +13396,7 @@
       </c>
       <c r="C763" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -13447,7 +13447,7 @@
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -13515,7 +13515,7 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -13719,7 +13719,7 @@
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -13889,7 +13889,7 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -13940,7 +13940,7 @@
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -13957,7 +13957,7 @@
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -13991,7 +13991,7 @@
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -14008,7 +14008,7 @@
       </c>
       <c r="C799" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -14348,7 +14348,7 @@
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -14365,7 +14365,7 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -14467,7 +14467,7 @@
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -14501,7 +14501,7 @@
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -14671,7 +14671,7 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -14773,7 +14773,7 @@
       </c>
       <c r="C844" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -14909,7 +14909,7 @@
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -14926,7 +14926,7 @@
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -15164,7 +15164,7 @@
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -15283,7 +15283,7 @@
       </c>
       <c r="C874" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -15487,7 +15487,7 @@
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -15776,7 +15776,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -15793,7 +15793,7 @@
       </c>
       <c r="C904" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -15861,7 +15861,7 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -15946,7 +15946,7 @@
       </c>
       <c r="C913" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -16031,7 +16031,7 @@
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -16048,7 +16048,7 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -16167,7 +16167,7 @@
       </c>
       <c r="C926" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -16184,7 +16184,7 @@
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -16201,7 +16201,7 @@
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -16286,7 +16286,7 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -16473,7 +16473,7 @@
       </c>
       <c r="C944" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -16830,7 +16830,7 @@
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -16898,7 +16898,7 @@
       </c>
       <c r="C969" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -16915,7 +16915,7 @@
       </c>
       <c r="C970" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -17051,7 +17051,7 @@
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -17068,7 +17068,7 @@
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -17476,7 +17476,7 @@
       </c>
       <c r="C1003" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -17663,7 +17663,7 @@
       </c>
       <c r="C1014" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -17680,7 +17680,7 @@
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -17765,7 +17765,7 @@
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -17918,7 +17918,7 @@
       </c>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18020,7 +18020,7 @@
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -18054,7 +18054,7 @@
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -18105,7 +18105,7 @@
       </c>
       <c r="C1040" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -18258,7 +18258,7 @@
       </c>
       <c r="C1049" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18292,7 +18292,7 @@
       </c>
       <c r="C1051" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18326,7 +18326,7 @@
       </c>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18377,7 +18377,7 @@
       </c>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18513,7 +18513,7 @@
       </c>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18530,7 +18530,7 @@
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18547,7 +18547,7 @@
       </c>
       <c r="C1066" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18564,7 +18564,7 @@
       </c>
       <c r="C1067" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18598,7 +18598,7 @@
       </c>
       <c r="C1069" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18632,7 +18632,7 @@
       </c>
       <c r="C1071" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18649,7 +18649,7 @@
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18700,7 +18700,7 @@
       </c>
       <c r="C1075" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -18734,7 +18734,7 @@
       </c>
       <c r="C1077" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -18802,7 +18802,7 @@
       </c>
       <c r="C1081" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18853,7 +18853,7 @@
       </c>
       <c r="C1084" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -18989,7 +18989,7 @@
       </c>
       <c r="C1092" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -19040,7 +19040,7 @@
       </c>
       <c r="C1095" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -19091,7 +19091,7 @@
       </c>
       <c r="C1098" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -19142,7 +19142,7 @@
       </c>
       <c r="C1101" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -19193,7 +19193,7 @@
       </c>
       <c r="C1104" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -19210,7 +19210,7 @@
       </c>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -19244,7 +19244,7 @@
       </c>
       <c r="C1107" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -19278,7 +19278,7 @@
       </c>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -19312,7 +19312,7 @@
       </c>
       <c r="C1111" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -19346,7 +19346,7 @@
       </c>
       <c r="C1113" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -19363,7 +19363,7 @@
       </c>
       <c r="C1114" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -19431,7 +19431,7 @@
       </c>
       <c r="C1118" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -19465,7 +19465,7 @@
       </c>
       <c r="C1120" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -19499,7 +19499,7 @@
       </c>
       <c r="C1122" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -19516,7 +19516,7 @@
       </c>
       <c r="C1123" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -19567,7 +19567,7 @@
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -19618,7 +19618,7 @@
       </c>
       <c r="C1129" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -19635,7 +19635,7 @@
       </c>
       <c r="C1130" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -19686,7 +19686,7 @@
       </c>
       <c r="C1133" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -19720,7 +19720,7 @@
       </c>
       <c r="C1135" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -19771,7 +19771,7 @@
       </c>
       <c r="C1138" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>SECURITY</t>
         </is>
       </c>
     </row>
@@ -19822,7 +19822,7 @@
       </c>
       <c r="C1141" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -19873,7 +19873,7 @@
       </c>
       <c r="C1144" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -19924,7 +19924,7 @@
       </c>
       <c r="C1147" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -19992,7 +19992,7 @@
       </c>
       <c r="C1151" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -20009,7 +20009,7 @@
       </c>
       <c r="C1152" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -20128,7 +20128,7 @@
       </c>
       <c r="C1159" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -20230,7 +20230,7 @@
       </c>
       <c r="C1165" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -20247,7 +20247,7 @@
       </c>
       <c r="C1166" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -20264,7 +20264,7 @@
       </c>
       <c r="C1167" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -20315,7 +20315,7 @@
       </c>
       <c r="C1170" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -20332,7 +20332,7 @@
       </c>
       <c r="C1171" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -20400,7 +20400,7 @@
       </c>
       <c r="C1175" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -20519,7 +20519,7 @@
       </c>
       <c r="C1182" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -20536,7 +20536,7 @@
       </c>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -20570,7 +20570,7 @@
       </c>
       <c r="C1185" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -20621,7 +20621,7 @@
       </c>
       <c r="C1188" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -20672,7 +20672,7 @@
       </c>
       <c r="C1191" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -20723,7 +20723,7 @@
       </c>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -20808,7 +20808,7 @@
       </c>
       <c r="C1199" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -20842,7 +20842,7 @@
       </c>
       <c r="C1201" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -20944,7 +20944,7 @@
       </c>
       <c r="C1207" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -21080,7 +21080,7 @@
       </c>
       <c r="C1215" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="C1217" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -21131,7 +21131,7 @@
       </c>
       <c r="C1218" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -21216,7 +21216,7 @@
       </c>
       <c r="C1223" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -21250,7 +21250,7 @@
       </c>
       <c r="C1225" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -21318,7 +21318,7 @@
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -21335,7 +21335,7 @@
       </c>
       <c r="C1230" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -21420,7 +21420,7 @@
       </c>
       <c r="C1235" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -21505,7 +21505,7 @@
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -21743,7 +21743,7 @@
       </c>
       <c r="C1254" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -21964,7 +21964,7 @@
       </c>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -22100,7 +22100,7 @@
       </c>
       <c r="C1275" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -22202,7 +22202,7 @@
       </c>
       <c r="C1281" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -22287,7 +22287,7 @@
       </c>
       <c r="C1286" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22321,7 +22321,7 @@
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -22372,7 +22372,7 @@
       </c>
       <c r="C1291" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -22406,7 +22406,7 @@
       </c>
       <c r="C1293" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C1294" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -22440,7 +22440,7 @@
       </c>
       <c r="C1295" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22457,7 +22457,7 @@
       </c>
       <c r="C1296" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -22491,7 +22491,7 @@
       </c>
       <c r="C1298" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -22593,7 +22593,7 @@
       </c>
       <c r="C1304" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -22610,7 +22610,7 @@
       </c>
       <c r="C1305" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22950,7 +22950,7 @@
       </c>
       <c r="C1325" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22967,7 +22967,7 @@
       </c>
       <c r="C1326" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -23086,7 +23086,7 @@
       </c>
       <c r="C1333" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -23120,7 +23120,7 @@
       </c>
       <c r="C1335" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -23137,7 +23137,7 @@
       </c>
       <c r="C1336" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -23154,7 +23154,7 @@
       </c>
       <c r="C1337" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -23205,7 +23205,7 @@
       </c>
       <c r="C1340" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -23239,7 +23239,7 @@
       </c>
       <c r="C1342" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -23273,7 +23273,7 @@
       </c>
       <c r="C1344" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -23426,7 +23426,7 @@
       </c>
       <c r="C1353" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -23460,7 +23460,7 @@
       </c>
       <c r="C1355" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -23528,7 +23528,7 @@
       </c>
       <c r="C1359" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -23545,7 +23545,7 @@
       </c>
       <c r="C1360" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -23579,7 +23579,7 @@
       </c>
       <c r="C1362" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -23596,7 +23596,7 @@
       </c>
       <c r="C1363" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -23613,7 +23613,7 @@
       </c>
       <c r="C1364" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -23630,7 +23630,7 @@
       </c>
       <c r="C1365" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -23664,7 +23664,7 @@
       </c>
       <c r="C1367" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -23681,7 +23681,7 @@
       </c>
       <c r="C1368" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -23715,7 +23715,7 @@
       </c>
       <c r="C1370" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -23732,7 +23732,7 @@
       </c>
       <c r="C1371" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="C1377" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24276,7 +24276,7 @@
       </c>
       <c r="C1403" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24395,7 +24395,7 @@
       </c>
       <c r="C1410" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24531,7 +24531,7 @@
       </c>
       <c r="C1418" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24735,7 +24735,7 @@
       </c>
       <c r="C1430" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24752,7 +24752,7 @@
       </c>
       <c r="C1431" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24820,7 +24820,7 @@
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24854,7 +24854,7 @@
       </c>
       <c r="C1437" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -24990,7 +24990,7 @@
       </c>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -25007,7 +25007,7 @@
       </c>
       <c r="C1446" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -25109,7 +25109,7 @@
       </c>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -25143,7 +25143,7 @@
       </c>
       <c r="C1454" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -25160,7 +25160,7 @@
       </c>
       <c r="C1455" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -25177,7 +25177,7 @@
       </c>
       <c r="C1456" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -25364,7 +25364,7 @@
       </c>
       <c r="C1467" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -25381,7 +25381,7 @@
       </c>
       <c r="C1468" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -25500,7 +25500,7 @@
       </c>
       <c r="C1475" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -25585,7 +25585,7 @@
       </c>
       <c r="C1480" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -25653,7 +25653,7 @@
       </c>
       <c r="C1484" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -25755,7 +25755,7 @@
       </c>
       <c r="C1490" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -25806,7 +25806,7 @@
       </c>
       <c r="C1493" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -25891,7 +25891,7 @@
       </c>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -25925,7 +25925,7 @@
       </c>
       <c r="C1500" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -26095,7 +26095,7 @@
       </c>
       <c r="C1510" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -26231,7 +26231,7 @@
       </c>
       <c r="C1518" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -26333,7 +26333,7 @@
       </c>
       <c r="C1524" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -26350,7 +26350,7 @@
       </c>
       <c r="C1525" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -26452,7 +26452,7 @@
       </c>
       <c r="C1531" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -26469,7 +26469,7 @@
       </c>
       <c r="C1532" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -26911,7 +26911,7 @@
       </c>
       <c r="C1558" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -27030,7 +27030,7 @@
       </c>
       <c r="C1565" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -27098,7 +27098,7 @@
       </c>
       <c r="C1569" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -27115,7 +27115,7 @@
       </c>
       <c r="C1570" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -27183,7 +27183,7 @@
       </c>
       <c r="C1574" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -27285,7 +27285,7 @@
       </c>
       <c r="C1580" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -27455,7 +27455,7 @@
       </c>
       <c r="C1590" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -27659,7 +27659,7 @@
       </c>
       <c r="C1602" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -27727,7 +27727,7 @@
       </c>
       <c r="C1606" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -27744,7 +27744,7 @@
       </c>
       <c r="C1607" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -27795,7 +27795,7 @@
       </c>
       <c r="C1610" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -27829,7 +27829,7 @@
       </c>
       <c r="C1612" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -28220,7 +28220,7 @@
       </c>
       <c r="C1635" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -28237,7 +28237,7 @@
       </c>
       <c r="C1636" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -28322,7 +28322,7 @@
       </c>
       <c r="C1641" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -28373,7 +28373,7 @@
       </c>
       <c r="C1644" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -28390,7 +28390,7 @@
       </c>
       <c r="C1645" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -28526,7 +28526,7 @@
       </c>
       <c r="C1653" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -28866,7 +28866,7 @@
       </c>
       <c r="C1673" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -28951,7 +28951,7 @@
       </c>
       <c r="C1678" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -29002,7 +29002,7 @@
       </c>
       <c r="C1681" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>SECURITY</t>
         </is>
       </c>
     </row>
@@ -29155,7 +29155,7 @@
       </c>
       <c r="C1690" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -29172,7 +29172,7 @@
       </c>
       <c r="C1691" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -29206,7 +29206,7 @@
       </c>
       <c r="C1693" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -29240,7 +29240,7 @@
       </c>
       <c r="C1695" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -29478,7 +29478,7 @@
       </c>
       <c r="C1709" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -29512,7 +29512,7 @@
       </c>
       <c r="C1711" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -29546,7 +29546,7 @@
       </c>
       <c r="C1713" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -29597,7 +29597,7 @@
       </c>
       <c r="C1716" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -29648,7 +29648,7 @@
       </c>
       <c r="C1719" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -29699,7 +29699,7 @@
       </c>
       <c r="C1722" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -29835,7 +29835,7 @@
       </c>
       <c r="C1730" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -29903,7 +29903,7 @@
       </c>
       <c r="C1734" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -29920,7 +29920,7 @@
       </c>
       <c r="C1735" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -29954,7 +29954,7 @@
       </c>
       <c r="C1737" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -30158,7 +30158,7 @@
       </c>
       <c r="C1749" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -30260,7 +30260,7 @@
       </c>
       <c r="C1755" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -30379,7 +30379,7 @@
       </c>
       <c r="C1762" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -30787,7 +30787,7 @@
       </c>
       <c r="C1786" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -30804,7 +30804,7 @@
       </c>
       <c r="C1787" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -30872,7 +30872,7 @@
       </c>
       <c r="C1791" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -30889,7 +30889,7 @@
       </c>
       <c r="C1792" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -30906,7 +30906,7 @@
       </c>
       <c r="C1793" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -30940,7 +30940,7 @@
       </c>
       <c r="C1795" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -31076,7 +31076,7 @@
       </c>
       <c r="C1803" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -31110,7 +31110,7 @@
       </c>
       <c r="C1805" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -31280,7 +31280,7 @@
       </c>
       <c r="C1815" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -31382,7 +31382,7 @@
       </c>
       <c r="C1821" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -31501,7 +31501,7 @@
       </c>
       <c r="C1828" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -31637,7 +31637,7 @@
       </c>
       <c r="C1836" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -31705,7 +31705,7 @@
       </c>
       <c r="C1840" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -31756,7 +31756,7 @@
       </c>
       <c r="C1843" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -31875,7 +31875,7 @@
       </c>
       <c r="C1850" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -32147,7 +32147,7 @@
       </c>
       <c r="C1866" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -32249,7 +32249,7 @@
       </c>
       <c r="C1872" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -32266,7 +32266,7 @@
       </c>
       <c r="C1873" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -32283,7 +32283,7 @@
       </c>
       <c r="C1874" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -32317,7 +32317,7 @@
       </c>
       <c r="C1876" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -32419,7 +32419,7 @@
       </c>
       <c r="C1882" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -32470,7 +32470,7 @@
       </c>
       <c r="C1885" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -32504,7 +32504,7 @@
       </c>
       <c r="C1887" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -32572,7 +32572,7 @@
       </c>
       <c r="C1891" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="C1894" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -32895,7 +32895,7 @@
       </c>
       <c r="C1910" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -33150,7 +33150,7 @@
       </c>
       <c r="C1925" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -33167,7 +33167,7 @@
       </c>
       <c r="C1926" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -33218,7 +33218,7 @@
       </c>
       <c r="C1929" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -33235,7 +33235,7 @@
       </c>
       <c r="C1930" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -33405,7 +33405,7 @@
       </c>
       <c r="C1940" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -33575,7 +33575,7 @@
       </c>
       <c r="C1950" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -33864,7 +33864,7 @@
       </c>
       <c r="C1967" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -33898,7 +33898,7 @@
       </c>
       <c r="C1969" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -33932,7 +33932,7 @@
       </c>
       <c r="C1971" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -33966,7 +33966,7 @@
       </c>
       <c r="C1973" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -34272,7 +34272,7 @@
       </c>
       <c r="C1991" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -34289,7 +34289,7 @@
       </c>
       <c r="C1992" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -34340,7 +34340,7 @@
       </c>
       <c r="C1995" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -34374,7 +34374,7 @@
       </c>
       <c r="C1997" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -34459,7 +34459,7 @@
       </c>
       <c r="C2002" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -34527,7 +34527,7 @@
       </c>
       <c r="C2006" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -34680,7 +34680,7 @@
       </c>
       <c r="C2015" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -34714,7 +34714,7 @@
       </c>
       <c r="C2017" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -34918,7 +34918,7 @@
       </c>
       <c r="C2029" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -35020,7 +35020,7 @@
       </c>
       <c r="C2035" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -35105,7 +35105,7 @@
       </c>
       <c r="C2040" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -35615,7 +35615,7 @@
       </c>
       <c r="C2070" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -35717,7 +35717,7 @@
       </c>
       <c r="C2076" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36040,7 +36040,7 @@
       </c>
       <c r="C2095" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36193,7 +36193,7 @@
       </c>
       <c r="C2104" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -36244,7 +36244,7 @@
       </c>
       <c r="C2107" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36397,7 +36397,7 @@
       </c>
       <c r="C2116" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -36448,7 +36448,7 @@
       </c>
       <c r="C2119" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36499,7 +36499,7 @@
       </c>
       <c r="C2122" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36584,7 +36584,7 @@
       </c>
       <c r="C2127" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36635,7 +36635,7 @@
       </c>
       <c r="C2130" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36703,7 +36703,7 @@
       </c>
       <c r="C2134" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -36839,7 +36839,7 @@
       </c>
       <c r="C2142" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -36992,7 +36992,7 @@
       </c>
       <c r="C2151" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37043,7 +37043,7 @@
       </c>
       <c r="C2154" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37111,7 +37111,7 @@
       </c>
       <c r="C2158" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -37145,7 +37145,7 @@
       </c>
       <c r="C2160" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37213,7 +37213,7 @@
       </c>
       <c r="C2164" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -37298,7 +37298,7 @@
       </c>
       <c r="C2169" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37315,7 +37315,7 @@
       </c>
       <c r="C2170" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37502,7 +37502,7 @@
       </c>
       <c r="C2181" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37638,7 +37638,7 @@
       </c>
       <c r="C2189" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37689,7 +37689,7 @@
       </c>
       <c r="C2192" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37757,7 +37757,7 @@
       </c>
       <c r="C2196" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37808,7 +37808,7 @@
       </c>
       <c r="C2199" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -37876,7 +37876,7 @@
       </c>
       <c r="C2203" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -38063,7 +38063,7 @@
       </c>
       <c r="C2214" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -38148,7 +38148,7 @@
       </c>
       <c r="C2219" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -38284,7 +38284,7 @@
       </c>
       <c r="C2227" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -38318,7 +38318,7 @@
       </c>
       <c r="C2229" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -38335,7 +38335,7 @@
       </c>
       <c r="C2230" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -38403,7 +38403,7 @@
       </c>
       <c r="C2234" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -38488,7 +38488,7 @@
       </c>
       <c r="C2239" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -38539,7 +38539,7 @@
       </c>
       <c r="C2242" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -38879,7 +38879,7 @@
       </c>
       <c r="C2262" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -38913,7 +38913,7 @@
       </c>
       <c r="C2264" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -38947,7 +38947,7 @@
       </c>
       <c r="C2266" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39049,7 +39049,7 @@
       </c>
       <c r="C2272" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39066,7 +39066,7 @@
       </c>
       <c r="C2273" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39117,7 +39117,7 @@
       </c>
       <c r="C2276" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39134,7 +39134,7 @@
       </c>
       <c r="C2277" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39151,7 +39151,7 @@
       </c>
       <c r="C2278" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39440,7 +39440,7 @@
       </c>
       <c r="C2295" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -39491,7 +39491,7 @@
       </c>
       <c r="C2298" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39593,7 +39593,7 @@
       </c>
       <c r="C2304" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -39661,7 +39661,7 @@
       </c>
       <c r="C2308" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -39712,7 +39712,7 @@
       </c>
       <c r="C2311" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -39746,7 +39746,7 @@
       </c>
       <c r="C2313" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40120,7 +40120,7 @@
       </c>
       <c r="C2335" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40188,7 +40188,7 @@
       </c>
       <c r="C2339" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40205,7 +40205,7 @@
       </c>
       <c r="C2340" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40290,7 +40290,7 @@
       </c>
       <c r="C2345" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40307,7 +40307,7 @@
       </c>
       <c r="C2346" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40426,7 +40426,7 @@
       </c>
       <c r="C2353" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40443,7 +40443,7 @@
       </c>
       <c r="C2354" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40460,7 +40460,7 @@
       </c>
       <c r="C2355" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40562,7 +40562,7 @@
       </c>
       <c r="C2361" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40579,7 +40579,7 @@
       </c>
       <c r="C2362" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40698,7 +40698,7 @@
       </c>
       <c r="C2369" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40783,7 +40783,7 @@
       </c>
       <c r="C2374" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -40851,7 +40851,7 @@
       </c>
       <c r="C2378" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -41123,7 +41123,7 @@
       </c>
       <c r="C2394" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41140,7 +41140,7 @@
       </c>
       <c r="C2395" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41157,7 +41157,7 @@
       </c>
       <c r="C2396" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41208,7 +41208,7 @@
       </c>
       <c r="C2399" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41225,7 +41225,7 @@
       </c>
       <c r="C2400" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41242,7 +41242,7 @@
       </c>
       <c r="C2401" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41259,7 +41259,7 @@
       </c>
       <c r="C2402" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41276,7 +41276,7 @@
       </c>
       <c r="C2403" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41293,7 +41293,7 @@
       </c>
       <c r="C2404" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41327,7 +41327,7 @@
       </c>
       <c r="C2406" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41480,7 +41480,7 @@
       </c>
       <c r="C2415" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41497,7 +41497,7 @@
       </c>
       <c r="C2416" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41599,7 +41599,7 @@
       </c>
       <c r="C2422" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -41684,7 +41684,7 @@
       </c>
       <c r="C2427" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41701,7 +41701,7 @@
       </c>
       <c r="C2428" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -41735,7 +41735,7 @@
       </c>
       <c r="C2430" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -42347,7 +42347,7 @@
       </c>
       <c r="C2466" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -42381,7 +42381,7 @@
       </c>
       <c r="C2468" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -42602,7 +42602,7 @@
       </c>
       <c r="C2481" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -42636,7 +42636,7 @@
       </c>
       <c r="C2483" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -42670,7 +42670,7 @@
       </c>
       <c r="C2485" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -42942,7 +42942,7 @@
       </c>
       <c r="C2501" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -42959,7 +42959,7 @@
       </c>
       <c r="C2502" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -42976,7 +42976,7 @@
       </c>
       <c r="C2503" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -43061,7 +43061,7 @@
       </c>
       <c r="C2508" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -43197,7 +43197,7 @@
       </c>
       <c r="C2516" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -43214,7 +43214,7 @@
       </c>
       <c r="C2517" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -43282,7 +43282,7 @@
       </c>
       <c r="C2521" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -43333,7 +43333,7 @@
       </c>
       <c r="C2524" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -43418,7 +43418,7 @@
       </c>
       <c r="C2529" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -43520,7 +43520,7 @@
       </c>
       <c r="C2535" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -43707,7 +43707,7 @@
       </c>
       <c r="C2546" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -43894,7 +43894,7 @@
       </c>
       <c r="C2557" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -43911,7 +43911,7 @@
       </c>
       <c r="C2558" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -43962,7 +43962,7 @@
       </c>
       <c r="C2561" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -43979,7 +43979,7 @@
       </c>
       <c r="C2562" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -43996,7 +43996,7 @@
       </c>
       <c r="C2563" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -44217,7 +44217,7 @@
       </c>
       <c r="C2576" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -44336,7 +44336,7 @@
       </c>
       <c r="C2583" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -44506,7 +44506,7 @@
       </c>
       <c r="C2593" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -44540,7 +44540,7 @@
       </c>
       <c r="C2595" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -44693,7 +44693,7 @@
       </c>
       <c r="C2604" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -44846,7 +44846,7 @@
       </c>
       <c r="C2613" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -44965,7 +44965,7 @@
       </c>
       <c r="C2620" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -45067,7 +45067,7 @@
       </c>
       <c r="C2626" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -45084,7 +45084,7 @@
       </c>
       <c r="C2627" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -45101,7 +45101,7 @@
       </c>
       <c r="C2628" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -45390,7 +45390,7 @@
       </c>
       <c r="C2645" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -45713,7 +45713,7 @@
       </c>
       <c r="C2664" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -45917,7 +45917,7 @@
       </c>
       <c r="C2676" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -46342,7 +46342,7 @@
       </c>
       <c r="C2701" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -46444,7 +46444,7 @@
       </c>
       <c r="C2707" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -46461,7 +46461,7 @@
       </c>
       <c r="C2708" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -46682,7 +46682,7 @@
       </c>
       <c r="C2721" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -46767,7 +46767,7 @@
       </c>
       <c r="C2726" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -46818,7 +46818,7 @@
       </c>
       <c r="C2729" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -46835,7 +46835,7 @@
       </c>
       <c r="C2730" t="inlineStr">
         <is>
-          <t>SECURITY</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -46920,7 +46920,7 @@
       </c>
       <c r="C2735" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47209,7 +47209,7 @@
       </c>
       <c r="C2752" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47345,7 +47345,7 @@
       </c>
       <c r="C2760" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47362,7 +47362,7 @@
       </c>
       <c r="C2761" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47379,7 +47379,7 @@
       </c>
       <c r="C2762" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47413,7 +47413,7 @@
       </c>
       <c r="C2764" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -47430,7 +47430,7 @@
       </c>
       <c r="C2765" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -47515,7 +47515,7 @@
       </c>
       <c r="C2770" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47549,7 +47549,7 @@
       </c>
       <c r="C2772" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -47685,7 +47685,7 @@
       </c>
       <c r="C2780" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47702,7 +47702,7 @@
       </c>
       <c r="C2781" t="inlineStr">
         <is>
-          <t>BUG</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -47753,7 +47753,7 @@
       </c>
       <c r="C2784" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -47923,7 +47923,7 @@
       </c>
       <c r="C2794" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -48161,7 +48161,7 @@
       </c>
       <c r="C2808" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -48195,7 +48195,7 @@
       </c>
       <c r="C2810" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -48331,7 +48331,7 @@
       </c>
       <c r="C2818" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -48705,7 +48705,7 @@
       </c>
       <c r="C2840" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -48722,7 +48722,7 @@
       </c>
       <c r="C2841" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -48824,7 +48824,7 @@
       </c>
       <c r="C2847" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -48926,7 +48926,7 @@
       </c>
       <c r="C2853" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>FEATURE</t>
         </is>
       </c>
     </row>
@@ -49096,7 +49096,7 @@
       </c>
       <c r="C2863" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -49130,7 +49130,7 @@
       </c>
       <c r="C2865" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -49249,7 +49249,7 @@
       </c>
       <c r="C2872" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -49283,7 +49283,7 @@
       </c>
       <c r="C2874" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -49606,7 +49606,7 @@
       </c>
       <c r="C2893" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -49912,7 +49912,7 @@
       </c>
       <c r="C2911" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -50048,7 +50048,7 @@
       </c>
       <c r="C2919" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -50133,7 +50133,7 @@
       </c>
       <c r="C2924" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>USABILITY</t>
         </is>
       </c>
     </row>
@@ -50167,7 +50167,7 @@
       </c>
       <c r="C2926" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -50252,7 +50252,7 @@
       </c>
       <c r="C2931" t="inlineStr">
         <is>
-          <t>USABILITY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -50405,7 +50405,7 @@
       </c>
       <c r="C2940" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -50575,7 +50575,7 @@
       </c>
       <c r="C2950" t="inlineStr">
         <is>
-          <t>SECURITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -50966,7 +50966,7 @@
       </c>
       <c r="C2973" t="inlineStr">
         <is>
-          <t>ENERGY</t>
+          <t>PERFORMANCE</t>
         </is>
       </c>
     </row>
@@ -50983,7 +50983,7 @@
       </c>
       <c r="C2974" t="inlineStr">
         <is>
-          <t>SECURITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -51136,7 +51136,7 @@
       </c>
       <c r="C2983" t="inlineStr">
         <is>
-          <t>PERFORMANCE</t>
+          <t>ENERGY</t>
         </is>
       </c>
     </row>
@@ -51170,7 +51170,7 @@
       </c>
       <c r="C2985" t="inlineStr">
         <is>
-          <t>SECURITY</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -51479,7 +51479,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.452</v>
+        <v>0.4606666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -51489,7 +51489,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5349687864152795</v>
+        <v>0.5493439524335444</v>
       </c>
     </row>
     <row r="4">
@@ -51499,7 +51499,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4728877163818562</v>
+        <v>0.4664905587760349</v>
       </c>
     </row>
     <row r="5">
@@ -51509,7 +51509,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.59298904965778</v>
+        <v>0.6122653098425076</v>
       </c>
     </row>
     <row r="6">
@@ -51519,7 +51519,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6779767566499849</v>
+        <v>0.6871950377639252</v>
       </c>
     </row>
     <row r="7">
@@ -51529,7 +51529,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>748.1889146000001</v>
+        <v>1695.168934781999</v>
       </c>
     </row>
     <row r="8">
@@ -51539,7 +51539,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2493963048666667</v>
+        <v>0.5650563115939997</v>
       </c>
     </row>
   </sheetData>
